--- a/inputs/col/col_config.xlsx
+++ b/inputs/col/col_config.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="38">
   <si>
     <t xml:space="preserve">iso3</t>
   </si>
@@ -41,6 +41,99 @@
   </si>
   <si>
     <t xml:space="preserve">sheet_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro oferta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL-OfertaUtilizacionPreciosCorrientes-2024p.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro utilización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor agregado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadro 22</t>
   </si>
 </sst>
 </file>
@@ -55,6 +148,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -114,8 +208,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -143,37 +241,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -246,30 +344,798 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="41.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.04"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
